--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0113.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0113.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Sentry Construct</t>
+          <t>Công Trình Tuần Tra</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Dragon of Dirge</t>
+          <t>Rồng Than Khóc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Mourning Aix - Early Access</t>
+          <t>Aix Tang Tóc - Early Access</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Lampylumen Myriad - Early Access</t>
+          <t>Lampylumen Myriad - Truy cập sớm</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Bell-Borne Geochelone - Early Access</t>
+          <t>Rùa Địa Chuông - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Sentinel Jué - Early Access</t>
+          <t>Sentinel Jué - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Sentry Construct - Early Access</t>
+          <t>Công Trình Tuần Tra - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hecate  - Early Access</t>
+          <t>Hecate - Early Access</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Lá Cờ Không Bao Giờ Rơi</t>
+          <t>Ngọn Cờ Không Bao Giờ Sụp Đổ</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Mô phỏng Phòng thủ Thủy triều</t>
+          <t>Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>"Moonlit Revelation" Limited-Time Event</t>
+          <t>"Khải Huyền Dưới Ánh Trăng" - Sự kiện thời hạn</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>"Lament Recon: Người Lính Solaris" Sự Kiện Giới Hạn</t>
+          <t>"Sự Tích Bi Hùng: Chiến Binh Solaris" Sự kiện giới hạn thời gian</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>"Những Điều Kỳ Lạ ở Honami" Sự Kiện</t>
+          <t>"Sự Kiện 'Chuyện Lạ Ở Honami'"</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Fishing</t>
+          <t>Câu Cá</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Event Requests</t>
+          <t>Yêu Cầu Sự Kiện</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Quests</t>
+          <t>Nhiệm vụ</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Nhận Chỉ Mục Cập Nhật</t>
+          <t>Cập nhật Chỉ mục để nhận</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Hoàn Thành "Tình Yêu Trong Thời Gian Câu Cá"</t>
+          <t>Hoàn thành "Love in the Time of Fishing"</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Complete "Where Tất cả Fish Converge"</t>
+          <t>Hoàn thành "Nơi Vạn Cá Hội Tụ".</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Hoàn Thành "Ông Già và Cá Voi"</t>
+          <t>Hoàn thành "Ông Già và Cá Voi"</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Complete "Old Captain's Log"</t>
+          <t>Hoàn thành "Nhật Ký Thuyền Trưởng Cũ"</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Convert Powpuff</t>
+          <t>Chuyển Đổi Powpuff</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Cảng Riccioli: Cửa Hàng Bến Cảng</t>
+          <t>Cảng Riccioli: Cửa Hàng Bến Tàu</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Làng Helm: Cửa Hàng Bến Cảng</t>
+          <t>Làng Helm: Cửa Hàng Bến Tàu</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Serene Bay: Cửa Hàng Bến Tàu</t>
+          <t>Vịnh Thanh Bình: Cửa Hàng Bến Tàu</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Reyes Ruins: Cửa Hàng Bến Tàu</t>
+          <t>Tàn Tích Reyes: Cửa Hàng Bến Tàu</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Ông Già và Cá Voi</t>
+          <t>Lão Già và Cá Voi</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Inferno Rider - Early Access</t>
+          <t>Kỵ Sĩ Hỏa Ngục - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Dragon of Dirge - Early Access</t>
+          <t>Rồng Than Khóc - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Ảo Tưởng Không Trở Lại - Early Access</t>
+          <t>Ảo Tưởng Vô Hồi - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Dreamless - Early Access</t>
+          <t>Vô Mộng - Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Kiếm Danh Tiếng trong Cuộc Đua Cubie</t>
+          <t>Thu thập Độ Nổi Tiếng trong Cuộc Đua Cubie</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Hoàn Thành Nhiệm Vụ Chính Chương II Hồi XI</t>
+          <t>Hoàn thành Chương II Hồi XI trong Nhiệm Vụ Chính</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Cubie Derby: Championship Keepsake Photo</t>
+          <t>Đua Cubie: Ảnh Lưu Niệm Giải Vô Địch</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>"Dawn upon Thorns" Set</t>
+          <t>"Bộ Dawn upon Thorns"</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Đã Đọc</t>
+          <t>Đọc</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Cùng nhau trong mưa cánh hoa</t>
+          <t>Cùng nhau trong Mưa Cánh Hoa</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Cùng nhau trong mưa cánh hoa</t>
+          <t>Cùng nhau trong Mưa Cánh Hoa</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>"Phantasma Dreamland" Event</t>
+          <t>"Sự kiện \"Phantasma Dreamland\""</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>"Where Stars Cascade Down" Event</t>
+          <t>"Sự Kiện \"Nơi Những Vì Sao Rơi\""</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Phần thưởng cột mốc Vibe Level</t>
+          <t>Phần Thưởng Cột Mốc Tần Số Vui Vẻ</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>The Lost Beyond</t>
+          <t>Vùng Đất Mất Tích</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Pilgrim's Scriptures</t>
+          <t>Kinh Thánh Hành Hương</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Crooked Doodles</t>
+          <t>Bức Vẽ Nguệch Ngoạc</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27665,7 +27665,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Giấy xác nhận: Hiệp hội Tiên phong</t>
+          <t>Thư Xác Nhận: Pioneer Association</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27735,7 +27735,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Crumpled Ghi chú</t>
+          <t>Mảnh Giấy Nhắn Vò Nát</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -28505,7 +28505,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Birthday Ghi chú</t>
+          <t>Lá Thư Sinh Nhật</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28575,7 +28575,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Một mảnh ghi chú từ nguồn không rõ</t>
+          <t>Lá Thư Từ Một Nguồn Không Rõ</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28645,7 +28645,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Bản viết bên dòng nước</t>
+          <t>Viết lách bên dòng nước</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28715,7 +28715,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>"The Thật sự Me"</t>
+          <t>"Bản Chất Thật Sự Của Tôi"</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
